--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00701-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00701-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{73C5B113-F117-486A-AB9D-E577174A929B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E21D8255-358E-4A63-A52E-60FC4FCA3F5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{D10BE8B6-DCDC-4661-A3AF-043BF7A9E65F}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{06297F5B-956F-4C4A-B1A3-0D78FD8EC34F}"/>
   </bookViews>
   <sheets>
     <sheet name="00701-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1528,25 +1528,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94FE2215-9F60-4097-B5A6-C200D3C33DD8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C907AE53-5D3E-4942-89D0-7B89D4B1F68C}">
   <dimension ref="A1:R26"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1574,7 +1574,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1604,7 +1604,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1650,7 +1650,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1700,7 +1700,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1754,7 +1754,7 @@
         <v>4.67</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1780,7 +1780,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>2.34</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
         <v>2025</v>
       </c>
@@ -1890,7 +1890,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -1946,7 +1946,7 @@
         <v>6.04</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -2002,7 +2002,7 @@
         <v>7.03</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="51">
         <v>2024</v>
       </c>
@@ -2056,7 +2056,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>27</v>
       </c>
@@ -2112,7 +2112,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>27</v>
       </c>
@@ -2168,7 +2168,7 @@
         <v>3.06</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="49">
         <v>2023</v>
       </c>
@@ -2222,7 +2222,7 @@
         <v>3.67</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>27</v>
       </c>
@@ -2278,7 +2278,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>27</v>
       </c>
@@ -2334,7 +2334,7 @@
         <v>2.91</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="51">
         <v>2022</v>
       </c>
@@ -2388,7 +2388,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>27</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>27</v>
       </c>
@@ -2500,7 +2500,7 @@
         <v>5.81</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="49">
         <v>2021</v>
       </c>
@@ -2554,7 +2554,7 @@
         <v>4.34</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>27</v>
       </c>
@@ -2610,7 +2610,7 @@
         <v>1.01</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>27</v>
       </c>
@@ -2666,7 +2666,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="51">
         <v>2020</v>
       </c>
@@ -2720,7 +2720,7 @@
         <v>6.61</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="49">
         <v>2019</v>
       </c>
@@ -2774,7 +2774,7 @@
         <v>2.21</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="51">
         <v>2018</v>
       </c>
@@ -2828,7 +2828,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="49" t="s">
         <v>47</v>
       </c>
